--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3288,16 +3288,120 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・GitHubDesktopのインストール</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>飯沼　世奈</t>
     <rPh sb="0" eb="2">
       <t>イイヌマ</t>
     </rPh>
     <rPh sb="3" eb="5">
       <t>セナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・GitHubDesktopのインストール
+・コイン、自販機、ゴミ箱アセット検索とゲームのアビリティ案＿完了
+・ゴミ箱(ゴール)のプログラムの作成＿作業途中
+訳）Unityで実験台の作成→ゴミ箱の中に入ったらログ出すようにする
+</t>
+    <rPh sb="27" eb="30">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>アン</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="87" eb="90">
+      <t>ジッケンダイ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="98" eb="99">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">GitHubの使い方の軽い説明、使用。
+グループでやることを分けして行った。ゲーム内容企画でのコインのアセット検索
+、自販機、ゴミ箱のアセット検索はみんなで共有できるようコメントにLinkを貼りました。また、毎回linkを見なくてもいいよう特徴を書きました。ゲームアビリティ案はWordに案をまとめてコメントに添付しました。
+</t>
+    <rPh sb="7" eb="8">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カル</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>マイカイ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="144" eb="145">
+      <t>アン</t>
+    </rPh>
+    <rPh sb="155" eb="157">
+      <t>テンプ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4301,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4338,10 +4442,12 @@
       <c r="A5" s="12">
         <v>46120</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="14"/>
+      <c r="B5" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>72</v>
+      </c>
       <c r="D5" s="15"/>
       <c r="E5" s="13"/>
     </row>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3402,6 +3402,61 @@
     </rPh>
     <rPh sb="155" eb="157">
       <t>テンプ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・情報共有。ドキュメント化は大切なので、積極的に続けてください。
+・シートの名前が「蒲池雅也」になっているので、自分のフルネームに書き換えてください。
+・翌日の予定の記載もお願いします。</t>
+    <rPh sb="1" eb="5">
+      <t>ジョウホウキョウユウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>タイセツ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>セッキョクテキ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="42" eb="46">
+      <t>カマチマサヤ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4448,8 +4503,12 @@
       <c r="C5" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="13"/>
+      <c r="D5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
       <c r="A6" s="12"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3402,6 +3402,151 @@
     </rPh>
     <rPh sb="155" eb="157">
       <t>テンプ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝に先生の説明の元デイリースクラムを行いました。
+昨日の途中だったゴミ箱のプログラムの作成を行いました。ゴミ箱の中に缶が入ったときにログが出るようにするため、透過した判定板を中に入れてタグ付けし判定ができるようにしました。効果音では、Unityアセットや効果音ラボ、スプリンギンなどの無料で使用できるもので探しました。</t>
+    <rPh sb="0" eb="1">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>トウカ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="111" eb="114">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="127" eb="130">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="142" eb="144">
+      <t>ムリョウ</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="153" eb="154">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・デイリースクラム。
+・ゴミ箱(ゴール)のプログラムの作成＿完了
+・効果音1(缶の音)、効果音2(車やコイン)の検索＿完了
+・ゴミ箱の上のスコア表示＿作業途中
+訳）UnityでUIをつける→見やすい色で行う</t>
+    <rPh sb="14" eb="15">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="44" eb="47">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="75" eb="79">
+      <t>サギョウトチュウ</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>オコナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4452,9 +4597,15 @@
       <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
-      <c r="A6" s="12"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="12">
+        <v>46121</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>73</v>
+      </c>
       <c r="D6" s="15"/>
       <c r="E6" s="13"/>
     </row>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -3489,63 +3489,66 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・デイリースクラム。
+    <t>・朝のデイリースクラム。
 ・ゴミ箱(ゴール)のプログラムの作成＿完了
 ・効果音1(缶の音)、効果音2(車やコイン)の検索＿完了
 ・ゴミ箱の上のスコア表示＿作業途中
 訳）UnityでUIをつける→見やすい色で行う</t>
-    <rPh sb="14" eb="15">
+    <rPh sb="1" eb="2">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
       <t>バコ</t>
     </rPh>
-    <rPh sb="27" eb="29">
+    <rPh sb="29" eb="31">
       <t>サクセイ</t>
     </rPh>
-    <rPh sb="30" eb="32">
+    <rPh sb="32" eb="34">
       <t>カンリョウ</t>
     </rPh>
-    <rPh sb="34" eb="37">
+    <rPh sb="36" eb="39">
       <t>コウカオン</t>
     </rPh>
-    <rPh sb="39" eb="40">
+    <rPh sb="41" eb="42">
       <t>カン</t>
     </rPh>
-    <rPh sb="41" eb="42">
+    <rPh sb="43" eb="44">
       <t>オト</t>
     </rPh>
-    <rPh sb="44" eb="47">
+    <rPh sb="46" eb="49">
       <t>コウカオン</t>
     </rPh>
-    <rPh sb="49" eb="50">
+    <rPh sb="51" eb="52">
       <t>クルマ</t>
     </rPh>
-    <rPh sb="56" eb="58">
+    <rPh sb="58" eb="60">
       <t>ケンサク</t>
     </rPh>
-    <rPh sb="59" eb="61">
+    <rPh sb="61" eb="63">
       <t>カンリョウ</t>
     </rPh>
-    <rPh sb="65" eb="66">
+    <rPh sb="67" eb="68">
       <t>バコ</t>
     </rPh>
-    <rPh sb="67" eb="68">
+    <rPh sb="69" eb="70">
       <t>ウエ</t>
     </rPh>
-    <rPh sb="72" eb="74">
+    <rPh sb="74" eb="76">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="75" eb="79">
+    <rPh sb="77" eb="81">
       <t>サギョウトチュウ</t>
     </rPh>
-    <rPh sb="80" eb="81">
+    <rPh sb="82" eb="83">
       <t>ヤク</t>
     </rPh>
-    <rPh sb="95" eb="96">
+    <rPh sb="97" eb="98">
       <t>ミ</t>
     </rPh>
-    <rPh sb="99" eb="100">
+    <rPh sb="101" eb="102">
       <t>イロ</t>
     </rPh>
-    <rPh sb="101" eb="102">
+    <rPh sb="103" eb="104">
       <t>オコナ</t>
     </rPh>
     <phoneticPr fontId="1"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,7 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
-    <sheet name="蒲池雅也" sheetId="2" r:id="rId2"/>
+    <sheet name="飯沼世奈" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3551,6 +3551,18 @@
     <rPh sb="103" eb="104">
       <t>オコナ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・翌営業日の予定の記載をお願いします。
+・作業項目を一つ一つ終わらせていくことが大切です。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3668,7 +3680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3718,6 +3730,9 @@
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4536,19 +4551,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="3" width="58.625" customWidth="1"/>
     <col min="5" max="5" width="42.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
@@ -4556,7 +4571,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -4573,7 +4588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="108" customHeight="1">
+    <row r="4" spans="1:6" ht="108" customHeight="1">
       <c r="A4" s="17">
         <v>46119</v>
       </c>
@@ -4586,7 +4601,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" ht="108" customHeight="1">
+    <row r="5" spans="1:6" ht="108" customHeight="1">
       <c r="A5" s="12">
         <v>46120</v>
       </c>
@@ -4599,7 +4614,7 @@
       <c r="D5" s="15"/>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" spans="1:5" ht="108" customHeight="1">
+    <row r="6" spans="1:6" ht="108" customHeight="1">
       <c r="A6" s="12">
         <v>46121</v>
       </c>
@@ -4609,73 +4624,78 @@
       <c r="C6" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" spans="1:5" ht="108" customHeight="1">
+      <c r="D6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="18"/>
+    </row>
+    <row r="7" spans="1:6" ht="108" customHeight="1">
       <c r="A7" s="12"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="15"/>
       <c r="E7" s="13"/>
     </row>
-    <row r="8" spans="1:5" ht="108" customHeight="1">
+    <row r="8" spans="1:6" ht="108" customHeight="1">
       <c r="A8" s="12"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
       <c r="E8" s="13"/>
     </row>
-    <row r="9" spans="1:5" ht="108" customHeight="1">
+    <row r="9" spans="1:6" ht="108" customHeight="1">
       <c r="A9" s="12"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>
     </row>
-    <row r="10" spans="1:5" ht="108" customHeight="1">
+    <row r="10" spans="1:6" ht="108" customHeight="1">
       <c r="A10" s="12"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>
     </row>
-    <row r="11" spans="1:5" ht="108" customHeight="1">
+    <row r="11" spans="1:6" ht="108" customHeight="1">
       <c r="A11" s="12"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>
     </row>
-    <row r="12" spans="1:5" ht="108" customHeight="1">
+    <row r="12" spans="1:6" ht="108" customHeight="1">
       <c r="A12" s="12"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>
     </row>
-    <row r="13" spans="1:5" ht="108" customHeight="1">
+    <row r="13" spans="1:6" ht="108" customHeight="1">
       <c r="A13" s="12"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>
     </row>
-    <row r="14" spans="1:5" ht="108" customHeight="1">
+    <row r="14" spans="1:6" ht="108" customHeight="1">
       <c r="A14" s="12"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="15"/>
       <c r="E14" s="13"/>
     </row>
-    <row r="15" spans="1:5" ht="108" customHeight="1">
+    <row r="15" spans="1:6" ht="108" customHeight="1">
       <c r="A15" s="12"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="15"/>
       <c r="E15" s="13"/>
     </row>
-    <row r="16" spans="1:5" ht="108" customHeight="1">
+    <row r="16" spans="1:6" ht="108" customHeight="1">
       <c r="A16" s="12"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3551,6 +3551,28 @@
     <rPh sb="103" eb="104">
       <t>オコナ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・面接対策
+※ゴミ箱(ゴール)のプログラムの作成＿修正完了
+・ゴミ箱の上のスコア表示＿作業途中
+訳）UIの位置をobjectの上に調整する。
+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>午前の2限目に上岡先生と面接対策を行った。
+昨日に完了していたゴミ箱のプログラムで今日実行を行ったところ、1つだけ不具合でログが表示されない問題が発生したので、objectの操作を見直して修正を行いました。また、ゴミ箱の上のスコア表示に関してはネットやコパイロットを使用したがobjectとUIが離れた位置で固定されてしまっているので調整し、次回には完了できるようにする。UIの配色の合わせはできそうであれば外観と合わせて検討する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・翌営業日の予定の記載をお願いします。
+・作業項目を一つ一つ終わらせていくことが大切です。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4609,13 +4631,23 @@
       <c r="C6" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="13"/>
+      <c r="D6" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
-      <c r="A7" s="12"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
+      <c r="A7" s="12">
+        <v>46122</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="D7" s="15"/>
       <c r="E7" s="13"/>
     </row>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,7 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
-    <sheet name="蒲池雅也" sheetId="2" r:id="rId2"/>
+    <sheet name="飯沼世奈" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="81">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3571,8 +3571,60 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>蒲池</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>・翌営業日の予定の記載をお願いします。
 ・作業項目を一つ一つ終わらせていくことが大切です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ログが表示されない問題　もチケットにしてしまって別のタスクとして扱ってもいいですよ。
+　チケットを作るのも時間がかかるので、必ず分ける必要はないですが、別のまとまりの仕事は別のチケットにするようにすると、後々管理しやすくなるので、検討してみてください。
+・翌営業日の予定の記載をお願いします。</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アツカ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="103" eb="107">
+      <t>ノチノチカンリ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>ケントウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4635,7 +4687,7 @@
         <v>77</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
@@ -4648,8 +4700,12 @@
       <c r="C7" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="13"/>
+      <c r="D7" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="108" customHeight="1">
       <c r="A8" s="12"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="90">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3625,6 +3625,53 @@
     <rPh sb="116" eb="118">
       <t>ケントウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・面接当日(家)
+・ゴミ箱の上のスコア表示＿(本日まで)
+訳）UIの位置をobjectの上に修正する。
+・飲料画像のUI＿
+訳）自分でアイビスで描く(本日まで)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・面接対策、練習
+・ゴミ箱の上のスコア表示＿作業途中(14日まで)
+訳）UIの位置をobjectの上に修正する。
+・飲料画像のUI＿未途中
+訳）自分でアイビスで描く(14日まで)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/14(火)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/13(月)</t>
+  </si>
+  <si>
+    <t>2026/4/10(金)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/8(水)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/9(木)</t>
+    <rPh sb="9" eb="10">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/7(火)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2限と4限目に上岡先生と面接対策を行いました。再度、会社について調べたり、大原の就職サポートを見て先輩方の就職試験体験談をもとに当たりやすい面接の質問の返答内容について考えました。
+ゴミ箱の上のスコア表示は手つかずでしたが、飲飲料画像をフリーで調べたところログインなどがめんどくさそうだったため、アイビスペイントでデフォルメっぽく描くことにしました。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4648,8 +4695,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="108" customHeight="1">
-      <c r="A4" s="17">
-        <v>46119</v>
+      <c r="A4" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>68</v>
@@ -4661,8 +4708,8 @@
       <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" ht="108" customHeight="1">
-      <c r="A5" s="12">
-        <v>46120</v>
+      <c r="A5" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>71</v>
@@ -4674,8 +4721,8 @@
       <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
-      <c r="A6" s="12">
-        <v>46121</v>
+      <c r="A6" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>74</v>
@@ -4691,8 +4738,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
-      <c r="A7" s="12">
-        <v>46122</v>
+      <c r="A7" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>75</v>
@@ -4708,15 +4755,25 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="108" customHeight="1">
-      <c r="A8" s="12"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
+      <c r="A8" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="D8" s="15"/>
       <c r="E8" s="13"/>
     </row>
     <row r="9" spans="1:5" ht="108" customHeight="1">
-      <c r="A9" s="12"/>
-      <c r="B9" s="14"/>
+      <c r="A9" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3672,6 +3672,39 @@
   <si>
     <t>2限と4限目に上岡先生と面接対策を行いました。再度、会社について調べたり、大原の就職サポートを見て先輩方の就職試験体験談をもとに当たりやすい面接の質問の返答内容について考えました。
 ゴミ箱の上のスコア表示は手つかずでしたが、飲飲料画像をフリーで調べたところログインなどがめんどくさそうだったため、アイビスペイントでデフォルメっぽく描くことにしました。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・Adobe のアプリ(Photoshop/illustrator)も使えるので、そちらの方が良ければ相談してください。
+　2026年版インストール対応中なので先にインストール対応できます。</t>
+    <rPh sb="35" eb="36">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ソウダン</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ネンバン</t>
+    </rPh>
+    <rPh sb="74" eb="77">
+      <t>タイオウチュウ</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>タイオウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4764,8 +4797,12 @@
       <c r="C8" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="13"/>
+      <c r="D8" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="108" customHeight="1">
       <c r="A9" s="12" t="s">

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3628,14 +3628,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・面接当日(家)
-・ゴミ箱の上のスコア表示＿(本日まで)
-訳）UIの位置をobjectの上に修正する。
-・飲料画像のUI＿
-訳）自分でアイビスで描く(本日まで)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・面接対策、練習
 ・ゴミ箱の上のスコア表示＿作業途中(14日まで)
 訳）UIの位置をobjectの上に修正する。
@@ -3707,12 +3699,176 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <r>
+      <t>・面接当日(家)
+・ゴミ箱の上のスコア表示＿作業途中(本日まで)→延長
+訳）UIの位置をobjectの上に修正する。
+・飲料画像のUI＿未途中
+訳）自分でアイビスで描く(本日まで)
+・自販機で取得できる能力＿作業途中(未)
+訳）飲料能力の実装するための表づくり→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>優先</t>
+    </r>
+    <rPh sb="22" eb="26">
+      <t>サギョウトチュウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>エンチョウ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="92" eb="95">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="104" eb="108">
+      <t>サギョウトチュウ</t>
+    </rPh>
+    <rPh sb="109" eb="110">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="112" eb="113">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>インリョウ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="119" eb="121">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="126" eb="127">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>ユウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2限あたりで家で面接を行いました。
+4限の5分過ぎからきてグループの人から進捗状況と優先してやってほしいことについて、説明を受けました。Ticket‘ｓの中に新しくやることを書き足してから、以前完了させたゲームのアビリティ案を基にして、ドリンクの名前、種類、能力、使用する画像またはイラストなどを再度考え、Excelの表にまとめを行いました。
+Adobe の件ありがとうございます。難しそうでありれば相談させていただきます。</t>
+    <rPh sb="6" eb="7">
+      <t>イエ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>フンス</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="37" eb="41">
+      <t>シンチョクジョウキョウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>イゼン</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>アン</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="136" eb="138">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="148" eb="150">
+      <t>サイド</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="159" eb="160">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="165" eb="166">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="179" eb="180">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="191" eb="192">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="200" eb="202">
+      <t>ソウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3774,6 +3930,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -3822,7 +3985,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3872,6 +4035,9 @@
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4729,7 +4895,7 @@
     </row>
     <row r="4" spans="1:5" ht="108" customHeight="1">
       <c r="A4" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>68</v>
@@ -4742,7 +4908,7 @@
     </row>
     <row r="5" spans="1:5" ht="108" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>71</v>
@@ -4755,7 +4921,7 @@
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>74</v>
@@ -4772,7 +4938,7 @@
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>75</v>
@@ -4789,29 +4955,31 @@
     </row>
     <row r="8" spans="1:5" ht="108" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="108" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="14"/>
+        <v>91</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>92</v>
+      </c>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>
     </row>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="95">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3860,6 +3860,21 @@
     </rPh>
     <rPh sb="200" eb="202">
       <t>ソウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・きちんと情報共有できているようで安心しました。
+・翌営業日の予定の記載をお願いします。</t>
+    <rPh sb="5" eb="9">
+      <t>ジョウホウキョウユウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>アンシン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4980,8 +4995,12 @@
       <c r="C9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="13"/>
+      <c r="D9" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="108" customHeight="1">
       <c r="A10" s="12"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="98">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3875,6 +3875,110 @@
     </rPh>
     <rPh sb="17" eb="19">
       <t>アンシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/15(水)</t>
+    <rPh sb="10" eb="11">
+      <t>スイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱の上のスコア表示＿作業途中
+訳）UIの位置をobjectの上に修正する。
+・飲料画像のUI＿完了
+訳）アイビス飲料イラストを描く
+・自販機で取得できる能力＿完了
+訳）飲料能力の実装するための表づくり</t>
+    <rPh sb="50" eb="52">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>インリョウ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>昨日の続きで、自販機で取得できる能力について表にまとめを行いました。ステータス強化なのか能力、ボーナス、リザルト強化かをしっかりと分けることができました。また、これが決まったことによってアイビスで、飲料の名前にちなんだイラストそれぞれを描きました。こちらは、しっかり表に○○.jpegを記載して今後使用するときにミスしないように取り組むことができました。ゴミ箱上のスコア表示がまだ途中なので今週中には完了させたい。</t>
+    <rPh sb="0" eb="2">
+      <t>サクジツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>インリョウ</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="118" eb="119">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="147" eb="151">
+      <t>コンゴシヨウ</t>
+    </rPh>
+    <rPh sb="164" eb="165">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="166" eb="167">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="179" eb="181">
+      <t>バコジョウ</t>
+    </rPh>
+    <rPh sb="185" eb="187">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="190" eb="192">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="195" eb="198">
+      <t>コンシュウチュウ</t>
+    </rPh>
+    <rPh sb="200" eb="202">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5003,9 +5107,15 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="108" customHeight="1">
-      <c r="A10" s="12"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
+      <c r="A10" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>
     </row>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="100">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3980,6 +3980,18 @@
     <rPh sb="200" eb="202">
       <t>カンリョウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/16(木)</t>
+    <rPh sb="10" eb="11">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱の上のスコア表示＿作業途中
+訳）UIの位置をobjectの上に修正する。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4104,7 +4116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4156,6 +4168,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5120,8 +5135,12 @@
       <c r="E10" s="13"/>
     </row>
     <row r="11" spans="1:5" ht="108" customHeight="1">
-      <c r="A11" s="12"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>99</v>
+      </c>
       <c r="C11" s="14"/>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3992,6 +3992,46 @@
   <si>
     <t>・ゴミ箱の上のスコア表示＿作業途中
 訳）UIの位置をobjectの上に修正する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・リソースや管理表もgit に入れて履歴管理してよさそうです。
+・ゴミ箱の上のスコア表示　チケットが見当たらないので、なければ作成を、すでにあるのであれば名前(TICKETS-??)を教えてください
+</t>
+    <rPh sb="6" eb="9">
+      <t>カンリヒョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>リレキカンリ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ミア</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>オシ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5131,8 +5171,12 @@
       <c r="C10" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="13"/>
+      <c r="D10" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="108" customHeight="1">
       <c r="A11" s="12" t="s">

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3990,11 +3990,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゴミ箱の上のスコア表示＿作業途中
-訳）UIの位置をobjectの上に修正する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>蒲池</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -4032,6 +4027,139 @@
     <rPh sb="92" eb="93">
       <t>オシ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝のデイリースクラムの議事録を行った。
+昨日の続きのゴミ箱上のスコア表示を行いました。とりあえず、ネットで調べて表示することと右回転をするような形で作ることができました。また、ゴミ箱のゴールは缶ではなく判定板につけるよう変更しました。ゴミ箱上のスコアとゴールしたときのスコアを同じように表示するために組みなおしています。
+ゴミ箱上のスコア表示はTIKETS-28です。</t>
+    <rPh sb="0" eb="1">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サクジツ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>バコジョウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>シラ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="63" eb="66">
+      <t>ミギカイテン</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="90" eb="91">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="101" eb="104">
+      <t>ハンテイイタ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="119" eb="121">
+      <t>バコジョウ</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="163" eb="165">
+      <t>バコジョウ</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱の上のスコア表示＿完了
+訳）UIの位置をobjectの上に修正する。
+※ゴミ箱(ゴール)のプログラムの作成＿修正完了②
+・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示_結合＿作業途中
+訳）以前完了したものとのスコアを同じく出すようにする。
+・議事録作成(係)</t>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="95" eb="99">
+      <t>サギョウトチュウ</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>イゼン</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="116" eb="117">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="119" eb="120">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="129" eb="132">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="135" eb="136">
+      <t>カカリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/17(金)</t>
+    <rPh sb="10" eb="11">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示_結合＿作業途中
+訳）以前完了したものとのスコアを同じく出すようにする。
+・議事録作成(係)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5172,10 +5300,10 @@
         <v>97</v>
       </c>
       <c r="D10" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>100</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="108" customHeight="1">
@@ -5183,15 +5311,21 @@
         <v>98</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>101</v>
+      </c>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>
     </row>
     <row r="12" spans="1:5" ht="108" customHeight="1">
-      <c r="A12" s="12"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>104</v>
+      </c>
       <c r="C12" s="14"/>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="106">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4160,6 +4160,20 @@
     <t>・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示_結合＿作業途中
 訳）以前完了したものとのスコアを同じく出すようにする。
 ・議事録作成(係)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・議事録ってどこにあります？
+・チケットの情報ありがとうございます。確認できました</t>
+    <rPh sb="1" eb="4">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カクニン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5316,8 +5330,12 @@
       <c r="C11" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="13"/>
+      <c r="D11" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="108" customHeight="1">
       <c r="A12" s="12" t="s">

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="109">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3886,24 +3886,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゴミ箱の上のスコア表示＿作業途中
-訳）UIの位置をobjectの上に修正する。
-・飲料画像のUI＿完了
-訳）アイビス飲料イラストを描く
-・自販機で取得できる能力＿完了
-訳）飲料能力の実装するための表づくり</t>
-    <rPh sb="50" eb="52">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>インリョウ</t>
-    </rPh>
-    <rPh sb="82" eb="84">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>昨日の続きで、自販機で取得できる能力について表にまとめを行いました。ステータス強化なのか能力、ボーナス、リザルト強化かをしっかりと分けることができました。また、これが決まったことによってアイビスで、飲料の名前にちなんだイラストそれぞれを描きました。こちらは、しっかり表に○○.jpegを記載して今後使用するときにミスしないように取り組むことができました。ゴミ箱上のスコア表示がまだ途中なので今週中には完了させたい。</t>
     <rPh sb="0" eb="2">
       <t>サクジツ</t>
@@ -4157,12 +4139,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示_結合＿作業途中
-訳）以前完了したものとのスコアを同じく出すようにする。
-・議事録作成(係)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・議事録ってどこにあります？
 ・チケットの情報ありがとうございます。確認できました</t>
     <rPh sb="1" eb="4">
@@ -4173,6 +4149,153 @@
     </rPh>
     <rPh sb="34" eb="36">
       <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱の上のスコア表示＿作業途中
+訳）UIの位置をobjectの上に修正する。
+・飲料画像のUI＿完了
+訳）アイビス飲料イラストを描く
+・自販機で買える能力表＿完了
+訳）飲料能力の実装するための表づくり</t>
+    <rPh sb="50" eb="52">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>インリョウ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="77" eb="80">
+      <t>ノウリョクヒョウ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝のデイリースクラムの議事録を行った。
+ゴミ箱のゴールログと上に出るスコア表示をscoreValueで同じ数値が出るようにすることができました。新しく自販機で買える表を実装できるものできないもので改良して、しっかりまとめることができました。
+議事録は、GitHubのDeilyScrumの中に入っています。ついでα版の反省まとめなども入っています。</t>
+    <rPh sb="22" eb="23">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="75" eb="78">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>カイリョウ</t>
+    </rPh>
+    <rPh sb="121" eb="124">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="144" eb="145">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="146" eb="147">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="157" eb="158">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>ハンセイ</t>
+    </rPh>
+    <rPh sb="167" eb="168">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/20(月)</t>
+    <rPh sb="10" eb="11">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をobjectにつける。
+・議事録作成(係)</t>
+    <rPh sb="1" eb="4">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カカリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示_結合＿完了
+訳）以前完了したものとのスコアを同じく出すようにする。
+・自販機で買える能力表２＿完了
+・TIKETS-のまとめ＿随時
+・α版の反省、改善、目標まとめ＿完了
+・議事録作成(係)</t>
+    <rPh sb="31" eb="33">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="70" eb="73">
+      <t>ノウリョクヒョウ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ズイジ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>アルファバン</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ハンセイ</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5308,49 +5431,55 @@
         <v>95</v>
       </c>
       <c r="B10" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>97</v>
-      </c>
       <c r="D10" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>99</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="108" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="108" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="14"/>
+        <v>108</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>105</v>
+      </c>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>
     </row>
     <row r="13" spans="1:5" ht="108" customHeight="1">
-      <c r="A13" s="12"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>107</v>
+      </c>
       <c r="C13" s="14"/>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="110">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4296,6 +4296,35 @@
     </rPh>
     <rPh sb="110" eb="112">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・議事録確認しました。整理されててとても良いです
+・効果音が付くと、一段クオリティが上がるので、よろしくお願いしますね</t>
+    <rPh sb="1" eb="6">
+      <t>ギジロクカクニン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>イチダン</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5470,8 +5499,12 @@
       <c r="C12" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="13"/>
+      <c r="D12" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="108" customHeight="1">
       <c r="A13" s="12" t="s">

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="113">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4247,23 +4247,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・効果音をobjectにつける。
-・議事録作成(係)</t>
-    <rPh sb="1" eb="4">
-      <t>コウカオン</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>ギジロク</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>カカリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示_結合＿完了
 訳）以前完了したものとのスコアを同じく出すようにする。
 ・自販機で買える能力表２＿完了
@@ -4325,6 +4308,144 @@
     </rPh>
     <rPh sb="53" eb="54">
       <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音つける1(缶vol.1)＿途中
+・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示_結合(訂正)＿途中
+訳）スコアが建物を貫通してしまうのを直す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/21(火)</t>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・効果音をobjectにつける。
+→効果音つける1(缶vol.1)＿途中
+・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示_結合(訂正)＿途中→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>優先</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+訳）スコアが建物を貫通してしまうのを直す
+・TIKETS-の作成
+・議事録作成(係)</t>
+    </r>
+    <rPh sb="1" eb="4">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="112" eb="115">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="118" eb="119">
+      <t>カカリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝のデイリースクラムの議事録を行った。
+前回完了したものをプロジェクトに入れたところスコアが建物を貫通してしまうことが分かったため、スクリプトとインスペクターを見直して直す。また、効果音を1つのものを和kwて使いたいため切り取りを行おうとしたところで、検索していました。こちらに関しては小林さんのに合体させるためプレで作成を行う。</t>
+    <rPh sb="20" eb="24">
+      <t>ゼンカイカンリョウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ミナオ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="90" eb="93">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="139" eb="140">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>コバヤシ</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>ガッタイ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="162" eb="163">
+      <t>オコナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5494,7 +5615,7 @@
         <v>102</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>105</v>
@@ -5503,7 +5624,7 @@
         <v>77</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="108" customHeight="1">
@@ -5511,15 +5632,21 @@
         <v>106</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="14"/>
+        <v>111</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>112</v>
+      </c>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5" ht="108" customHeight="1">
-      <c r="A14" s="12"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>109</v>
+      </c>
       <c r="C14" s="14"/>
       <c r="D14" s="15"/>
       <c r="E14" s="13"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="119">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4309,12 +4309,6 @@
     <rPh sb="53" eb="54">
       <t>ネガ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・効果音つける1(缶vol.1)＿途中
-・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示_結合(訂正)＿途中
-訳）スコアが建物を貫通してしまうのを直す</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4446,6 +4440,137 @@
     </rPh>
     <rPh sb="162" eb="163">
       <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音つける1(缶vol.1)＿途中
+・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示_結合(訂正)＿完了
+訳）スコアが建物を貫通してしまうのを直す
+・議事録作成(係)</t>
+    <rPh sb="55" eb="57">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="80" eb="85">
+      <t>ギジロクサクセイ</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>カカリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝に議事録作成を行ったが、GitHubがうまく動かなかった。
+とりあえず昨日問題になっていた建物を貫通してしまうスコアは、worldsceneで３Dにして、直しました。回転するのをやめて、カメラに追従釣るような形になりました。効果音をつけるものは、1つの音を別々にカットしてつけるため、先生が入れてくださったAdibeでカットまではおわしたので、明日は缶に音をつけようと思います。</t>
+    <rPh sb="0" eb="1">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="36" eb="40">
+      <t>キノウモンダイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>カイテン</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ツイジュウ</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="105" eb="106">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="113" eb="116">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="127" eb="128">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>ベツベツ</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="146" eb="147">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="173" eb="175">
+      <t>アシタ</t>
+    </rPh>
+    <rPh sb="176" eb="177">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="178" eb="179">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="185" eb="186">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/22(水)</t>
+    <rPh sb="10" eb="11">
+      <t>スイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/23(木)</t>
+    <rPh sb="10" eb="11">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/24(金)</t>
+    <rPh sb="10" eb="11">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/27(月)</t>
+    <rPh sb="10" eb="11">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音つける1(缶vol.1)＿
+訳）それぞれ用途に分けてつける
+・効果音つける2(缶vol.2)＿
+・議事録作成(係)</t>
+    <rPh sb="18" eb="19">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヨウト</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5632,48 +5757,60 @@
         <v>106</v>
       </c>
       <c r="B13" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>111</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>112</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5" ht="108" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="14"/>
+        <v>112</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>113</v>
+      </c>
       <c r="D14" s="15"/>
       <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:5" ht="108" customHeight="1">
-      <c r="A15" s="12"/>
-      <c r="B15" s="14"/>
+      <c r="A15" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="C15" s="14"/>
       <c r="D15" s="15"/>
       <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5" ht="108" customHeight="1">
-      <c r="A16" s="12"/>
+      <c r="A16" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5" ht="108" customHeight="1">
-      <c r="A17" s="12"/>
+      <c r="A17" s="12" t="s">
+        <v>116</v>
+      </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="15"/>
       <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5" ht="108" customHeight="1">
-      <c r="A18" s="12"/>
+      <c r="A18" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="15"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="120">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4559,18 +4559,78 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・効果音つける1(缶vol.1)＿
+    <t>・効果音つける1(缶vol.1)＿途中
 訳）それぞれ用途に分けてつける
-・効果音つける2(缶vol.2)＿
+・効果音つける2(缶vol.2)＿途中
+・TIKETS-の作成
 ・議事録作成(係)</t>
-    <rPh sb="18" eb="19">
+    <rPh sb="17" eb="19">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
       <t>ヤク</t>
     </rPh>
-    <rPh sb="24" eb="26">
+    <rPh sb="26" eb="28">
       <t>ヨウト</t>
     </rPh>
-    <rPh sb="27" eb="28">
+    <rPh sb="29" eb="30">
       <t>ワ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝にデイリースクラムの議事録を行った。TIKETS-の作成を再度書き直したり新しく増やしたりしました。
+効果音をつける時に実験として缶を入れようとしたらエラーになって小林さんに直してもらったところまでしか進みませんでした。</t>
+    <rPh sb="0" eb="1">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="30" eb="33">
+      <t>サイドカ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ジッケン</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>コバヤシ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="102" eb="103">
+      <t>スス</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5785,7 +5845,9 @@
       <c r="B15" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="14"/>
+      <c r="C15" s="14" t="s">
+        <v>119</v>
+      </c>
       <c r="D15" s="15"/>
       <c r="E15" s="13"/>
     </row>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="122">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4631,6 +4631,58 @@
     </rPh>
     <rPh sb="102" eb="103">
       <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・1限でトラブルが発生すると解決だけで終わってしまいますよね。
+・チーム内で解決できるのが理想ですが、私の方も使ってくれてかまわないので、声をかけてみてください
+・作業予定の記載もお願いします。</t>
+    <rPh sb="2" eb="3">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>リソウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>コエ</t>
+    </rPh>
+    <rPh sb="82" eb="86">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="91" eb="92">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5822,7 +5874,9 @@
       <c r="C13" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D13" s="15"/>
+      <c r="D13" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5" ht="108" customHeight="1">
@@ -5835,7 +5889,9 @@
       <c r="C14" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="15"/>
+      <c r="D14" s="15" t="s">
+        <v>77</v>
+      </c>
       <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:5" ht="108" customHeight="1">
@@ -5848,8 +5904,12 @@
       <c r="C15" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="13"/>
+      <c r="D15" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="108" customHeight="1">
       <c r="A16" s="12" t="s">

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="124">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4559,29 +4559,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・効果音つける1(缶vol.1)＿途中
-訳）それぞれ用途に分けてつける
-・効果音つける2(缶vol.2)＿途中
-・TIKETS-の作成
-・議事録作成(係)</t>
-    <rPh sb="17" eb="19">
-      <t>トチュウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ヤク</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ヨウト</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>トチュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>朝にデイリースクラムの議事録を行った。TIKETS-の作成を再度書き直したり新しく増やしたりしました。
 効果音をつける時に実験として缶を入れようとしたらエラーになって小林さんに直してもらったところまでしか進みませんでした。</t>
     <rPh sb="0" eb="1">
@@ -4683,6 +4660,58 @@
     </rPh>
     <rPh sb="91" eb="92">
       <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音つける1(缶vol.1)＿
+訳）それぞれ用途に分けてつける
+・効果音つける2(缶vol.3)＿
+・TIKETS-の作成
+・議事録作成(係)</t>
+    <rPh sb="18" eb="19">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヨウト</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音つける1(缶vol.1)＿途中
+訳）それぞれ用途に分けてつける
+・TIKETS-の作成
+・議事録作成(係)</t>
+    <rPh sb="17" eb="19">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヨウト</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音つける1(缶vol.1)＿
+訳）それぞれ用途に分けてつける
+・TIKETS-の作成
+・議事録作成(係)</t>
+    <rPh sb="18" eb="19">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヨウト</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5875,7 +5904,7 @@
         <v>111</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E13" s="13"/>
     </row>
@@ -5899,23 +5928,25 @@
         <v>114</v>
       </c>
       <c r="B15" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>118</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>119</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="108" customHeight="1">
       <c r="A16" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="14" t="s">
+        <v>123</v>
+      </c>
       <c r="C16" s="14"/>
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="125">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4664,23 +4664,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・効果音つける1(缶vol.1)＿
-訳）それぞれ用途に分けてつける
-・効果音つける2(缶vol.3)＿
-・TIKETS-の作成
-・議事録作成(係)</t>
-    <rPh sb="18" eb="19">
-      <t>ヤク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ヨウト</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・効果音つける1(缶vol.1)＿途中
 訳）それぞれ用途に分けてつける
 ・TIKETS-の作成
@@ -4700,17 +4683,144 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・効果音つける1(缶vol.1)＿
+    <t>朝にデイリースクラムの議事録を行った。
+効果音を2限で付けようとしたら、転がる音がイマイチつながりが悪く調整していたのと地面の時だけ鳴らすようにしようとして、途中になりました。また、ゴミ箱をプロジェクトに移動するにあたり、別のCanvasについてしまい画面に表示されない問題が発生したので明日は直せるようにしたいです。</t>
+    <rPh sb="0" eb="1">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>コロ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="135" eb="137">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="138" eb="140">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="144" eb="146">
+      <t>アシタ</t>
+    </rPh>
+    <rPh sb="147" eb="148">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱のプロジェクト移動＿
+・効果音つける1(缶vol.1)＿
+訳）それぞれ用途に分けてつける
+・議事録作成(係)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・ゴミ箱のプロジェクト移動＿途中→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>優先</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・効果音つける1(缶vol.1)＿途中→小林さんに譲渡しました
 訳）それぞれ用途に分けてつける
 ・TIKETS-の作成
 ・議事録作成(係)</t>
-    <rPh sb="18" eb="19">
+    </r>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>コバヤシ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ジョウト</t>
+    </rPh>
+    <rPh sb="52" eb="53">
       <t>ヤク</t>
     </rPh>
-    <rPh sb="24" eb="26">
+    <rPh sb="58" eb="60">
       <t>ヨウト</t>
     </rPh>
-    <rPh sb="27" eb="28">
+    <rPh sb="61" eb="62">
       <t>ワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -5928,7 +6038,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>118</v>
@@ -5945,9 +6055,11 @@
         <v>115</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="14"/>
+        <v>124</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>122</v>
+      </c>
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>
     </row>
@@ -5955,7 +6067,9 @@
       <c r="A17" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="14"/>
+      <c r="B17" s="14" t="s">
+        <v>123</v>
+      </c>
       <c r="C17" s="14"/>
       <c r="D17" s="15"/>
       <c r="E17" s="13"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="127">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4819,8 +4819,92 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゴミ箱のプロジェクト移動＿
+    <t>・ゴミ箱のプロジェクト移動＿完了
+・効果音をつける4(コイン)＿完了
+・ゲームBGMの作成＿途中
 ・議事録作成(係)</t>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームBGMの作成＿途中
+・議事録作成(係)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝にデイリースクラムの議事録を行った。
+ゴミ箱のプロジェクトを移動して、スコアの表示が貫通しないようにCanvasを別に分けて直しました。また、コインを取ったときに効果音が鳴るようにOdioをつけました。ゲームのBGMはゲーム中には付けられましたが、まだタイトル時に同じくつけたもののうまく動作していないので直したいです。</t>
+    <rPh sb="0" eb="1">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カンツウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="82" eb="85">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="116" eb="117">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="154" eb="155">
+      <t>ナオ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6068,7 +6152,9 @@
       <c r="B17" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="14"/>
+      <c r="C17" s="14" t="s">
+        <v>126</v>
+      </c>
       <c r="D17" s="15"/>
       <c r="E17" s="13"/>
     </row>
@@ -6076,7 +6162,9 @@
       <c r="A18" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="14"/>
+      <c r="B18" s="14" t="s">
+        <v>125</v>
+      </c>
       <c r="C18" s="14"/>
       <c r="D18" s="15"/>
       <c r="E18" s="13"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -5382,6 +5382,9 @@
       </c>
     </row>
     <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="D2" s="4" t="s">
         <v>1</v>
       </c>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -1748,6 +1748,11 @@
     <rPh sb="154" eb="155">
       <t>ナオ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・同じ対応でうまくいかないのが謎ですね。
+　一般論でいえば気づいていない差異があるってことですが、わからない場合は相談してください。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2442,8 +2447,12 @@
       <c r="C17" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="8"/>
+      <c r="D17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="108" customHeight="1">
       <c r="A18" s="7" t="s">

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -1662,33 +1662,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゴミ箱のプロジェクト移動＿完了
-・効果音をつける4(コイン)＿完了
-・ゲームBGMの作成＿途中
-・議事録作成(係)</t>
-    <rPh sb="14" eb="16">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>コウカオン</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>トチュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・ゲームBGMの作成＿途中
-・議事録作成(係)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>朝にデイリースクラムの議事録を行った。
 ゴミ箱のプロジェクトを移動して、スコアの表示が貫通しないようにCanvasを別に分けて直しました。また、コインを取ったときに効果音が鳴るようにOdioをつけました。ゲームのBGMはゲーム中には付けられましたが、まだタイトル時に同じくつけたもののうまく動作していないので直したいです。</t>
     <rPh sb="0" eb="1">
@@ -1753,6 +1726,219 @@
   <si>
     <t>・同じ対応でうまくいかないのが謎ですね。
 　一般論でいえば気づいていない差異があるってことですが、わからない場合は相談してください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱のプロジェクト移動＿完了
+・効果音をつける4(コイン)＿完了
+・ゲームBGMの再生＿途中
+・議事録作成(係)</t>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・ゲームBGMの再生＿完了
+・ゲーム説明制作＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="4"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・車の配置(案)＿未
+・効果音の切り取り＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="4"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">途中
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・TIKETS-の作成
+・β版の反省、改善、目標まとめ＿完了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・議事録作成(係)</t>
+    </r>
+    <rPh sb="11" eb="13">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/28(火)</t>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/5/7(木)</t>
+    <rPh sb="9" eb="10">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲーム説明制作＿
+・車の配置(案)＿
+・効果音の切り取り＿
+・議事録作成(係)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝に議事録と前回のβ版の反省・目標を書きました。
+ゲーム内のBGMをゲーム中とタイトルで分けて、スクリプトでスタートボタンが押された時にループして鳴るようにし、タイトルに戻ったときもしっかりBGMが変化するようにできました。ゲーム説明の制作は、GitHubの更新でBGMと共に消えてしまったため、画像で説明を制作することにしました。また、後からUnityに入れた時にボタンを配置し動くようにしようと思います。</t>
+    <rPh sb="0" eb="1">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゼンカイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハンセイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="148" eb="150">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="151" eb="153">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="169" eb="170">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="178" eb="179">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="181" eb="182">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="187" eb="189">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="190" eb="191">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="199" eb="200">
+      <t>オモ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1760,7 +1946,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1773,13 +1959,6 @@
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="4" tint="-0.249977111117893"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1822,8 +2001,40 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="4"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1840,6 +2051,21 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -1867,54 +2093,75 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="8" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="9" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="7" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="どちらでもない" xfId="3" builtinId="28"/>
+    <cellStyle name="悪い" xfId="2" builtinId="27"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="良い" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2233,7 +2480,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="108" customHeight="1">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="17" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -2246,7 +2493,7 @@
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" ht="108" customHeight="1">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -2259,7 +2506,7 @@
       <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="15" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -2276,7 +2523,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="15" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -2293,7 +2540,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="108" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="15" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -2310,13 +2557,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="108" customHeight="1">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -2327,7 +2574,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="108" customHeight="1">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="15" t="s">
         <v>34</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -2344,10 +2591,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="108" customHeight="1">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -2361,7 +2608,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="108" customHeight="1">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="15" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -2378,7 +2625,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="108" customHeight="1">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="16" t="s">
         <v>45</v>
       </c>
       <c r="B13" s="9" t="s">
@@ -2393,7 +2640,7 @@
       <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" ht="108" customHeight="1">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="16" t="s">
         <v>48</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -2408,7 +2655,7 @@
       <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" ht="108" customHeight="1">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="16" t="s">
         <v>53</v>
       </c>
       <c r="B15" s="9" t="s">
@@ -2425,7 +2672,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="108" customHeight="1">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="16" t="s">
         <v>54</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -2438,42 +2685,50 @@
       <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" ht="108" customHeight="1">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="16" t="s">
         <v>55</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>65</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="108" customHeight="1">
+      <c r="A18" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="108" customHeight="1">
-      <c r="A18" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="9"/>
+      <c r="C18" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="D18" s="10"/>
       <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" ht="108" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="9"/>
+      <c r="A19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="C19" s="9"/>
       <c r="D19" s="10"/>
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" ht="108" customHeight="1">
-      <c r="A20" s="7"/>
+      <c r="A20" s="14" t="s">
+        <v>68</v>
+      </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -1938,6 +1938,61 @@
     </rPh>
     <rPh sb="199" eb="200">
       <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・色が付いた！！
+・βの振り返りとても良いです。
+・Gitでの消失ですが、commit の履歴も消えているでしょうか？
+　Commit の履歴「GitHub Desktop で左下に入れているサマリーとコメント」が残っていれば、その時の状態を参照することはできるので、ご相談ください。</t>
+    <rPh sb="1" eb="2">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ショウシツ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ヒダリシタ</t>
+    </rPh>
+    <rPh sb="91" eb="92">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="107" eb="108">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="116" eb="117">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="135" eb="137">
+      <t>ソウダン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2711,8 +2766,12 @@
       <c r="C18" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="8"/>
+      <c r="D18" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="108" customHeight="1">
       <c r="A19" s="14" t="s">

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -1843,13 +1843,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゲーム説明制作＿
-・車の配置(案)＿
-・効果音の切り取り＿
-・議事録作成(係)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>朝に議事録と前回のβ版の反省・目標を書きました。
 ゲーム内のBGMをゲーム中とタイトルで分けて、スクリプトでスタートボタンが押された時にループして鳴るようにし、タイトルに戻ったときもしっかりBGMが変化するようにできました。ゲーム説明の制作は、GitHubの更新でBGMと共に消えてしまったため、画像で説明を制作することにしました。また、後からUnityに入れた時にボタンを配置し動くようにしようと思います。</t>
     <rPh sb="0" eb="1">
@@ -1994,6 +1987,171 @@
     <rPh sb="135" eb="137">
       <t>ソウダン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・ゲーム説明制作＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="4"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・車の配置(案)＿未
+・効果音の切り取り＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="4"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・議事録作成(係)</t>
+    </r>
+    <rPh sb="9" eb="11">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝にデイリースクラムの議事録を行った。
+ゲーム説明に入れる文と遊び方説明をアイビスペイントを使って作成し、画像は作ることができました。プロジェクトに入れて動かそうとしたら、Bottonとscriptの操作がうまく行えず、完了に至りませんでした。効果音は若干切り取るものがあると思うので、なんかあり次第切り取りを行おうと思います。
+Commitは消去ではないため残ってたと思いますが、履歴はありました。</t>
+    <rPh sb="0" eb="1">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>アソ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>カタセツメイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="122" eb="125">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>ジャッカン</t>
+    </rPh>
+    <rPh sb="128" eb="129">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="130" eb="131">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="148" eb="150">
+      <t>シダイ</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="152" eb="153">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="172" eb="174">
+      <t>ショウキョ</t>
+    </rPh>
+    <rPh sb="180" eb="181">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="185" eb="186">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="191" eb="193">
+      <t>リレキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲーム説明制作＿途中
+・車の配置(案)＿未
+・効果音の切り取り＿途中
+・議事録作成(係)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2764,13 +2922,13 @@
         <v>66</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="108" customHeight="1">
@@ -2778,9 +2936,11 @@
         <v>67</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>72</v>
+      </c>
       <c r="D19" s="10"/>
       <c r="E19" s="8"/>
     </row>
@@ -2788,7 +2948,9 @@
       <c r="A20" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="9"/>
+      <c r="B20" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
       <c r="E20" s="8"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="75">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -2152,6 +2152,46 @@
 ・車の配置(案)＿未
 ・効果音の切り取り＿途中
 ・議事録作成(係)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Commit のハッシュ値(→の赤丸をしたところの16進数数値）がわかれば、Commitしたときの状態に戻したり、Commitの変更のみ再度適用することはできるので、必要であれば相談してください。</t>
+    <rPh sb="12" eb="13">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>アカマル</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>サイド</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>ソウダン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2387,6 +2427,49 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>48375</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>962529</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>144031</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13602450" y="20879304"/>
+          <a:ext cx="6953656" cy="1837822"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2941,8 +3024,12 @@
       <c r="C19" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="8"/>
+      <c r="D19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="108" customHeight="1">
       <c r="A20" s="14" t="s">
@@ -3071,5 +3158,6 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -2148,9 +2148,117 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゲーム説明制作＿途中
-・車の配置(案)＿未
-・効果音の切り取り＿途中
+    <r>
+      <t>・ゲーム説明制作＿完了
+・効果音の切り取り＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="4"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・議事録作成(係)</t>
+    </r>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム説明を押したときにゲーム説明と操作方法に飛べるようにするのを完了することができました。ボタンを左右に押してページを切り替えることと、タイトルに戻るボタンも動くようになりました。Transfrompositionではなくlocalpositionを使うことで、ボタンを押したときに勝手に動くのを直すことができました。明日は効果音の確認と直しがあれば直せるようにしたいです。</t>
+    <rPh sb="3" eb="5">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>ソウサホウホウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="126" eb="127">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="142" eb="144">
+      <t>カッテ</t>
+    </rPh>
+    <rPh sb="145" eb="146">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="149" eb="150">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="160" eb="162">
+      <t>アシタ</t>
+    </rPh>
+    <rPh sb="163" eb="166">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="170" eb="171">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="176" eb="177">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/5/8(金)</t>
+    <rPh sb="9" eb="10">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音の切り取り＿途中
 ・議事録作成(係)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2951,13 +3059,19 @@
       <c r="B20" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="9"/>
+      <c r="C20" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="D20" s="10"/>
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="9"/>
+      <c r="A21" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="C21" s="9"/>
       <c r="D21" s="10"/>
       <c r="E21" s="8"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="78">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -2148,13 +2148,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゲーム説明制作＿途中
-・車の配置(案)＿未
-・効果音の切り取り＿途中
-・議事録作成(係)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Commit のハッシュ値(→の赤丸をしたところの16進数数値）がわかれば、Commitしたときの状態に戻したり、Commitの変更のみ再度適用することはできるので、必要であれば相談してください。</t>
     <rPh sb="12" eb="13">
       <t>アタイ</t>
@@ -2191,6 +2184,43 @@
     </rPh>
     <rPh sb="89" eb="91">
       <t>ソウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/5/8(金)</t>
+    <rPh sb="9" eb="10">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲーム説明制作＿完了
+・効果音の切り取り＿途中
+・議事録作成(係)</t>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝にデイリースクラムの議事録を行った。
+ゲーム説明を押したときにゲーム説明と操作方法に飛べるようにするのを完了することができました。ボタンを左右に押してページを切り替えることと、タイトルに戻るボタンも動くようになりました。Transfrompositionではなくlocalpositionを使うことで、ボタンを押したときに勝手に動くのを直すことができました。明日は効果音の確認と直しがあれば直せるようにしたいです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音の切り取り＿途中
+・BGMの実装＿未
+・fainal tester＿未
+・議事録作成(係)</t>
+    <rPh sb="18" eb="20">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ミ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3028,7 +3058,7 @@
         <v>16</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="108" customHeight="1">
@@ -3036,15 +3066,21 @@
         <v>68</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="9"/>
+        <v>75</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="D20" s="10"/>
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="9"/>
+      <c r="A21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="C21" s="9"/>
       <c r="D21" s="10"/>
       <c r="E21" s="8"/>

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="79">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -2221,6 +2221,23 @@
     </rPh>
     <rPh sb="38" eb="39">
       <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・議事録作成ありがとうございました。
+・残り一日、やれることをやっていきましょう。</t>
+    <rPh sb="1" eb="4">
+      <t>ギジロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イチニチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3071,8 +3088,12 @@
       <c r="C20" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="8"/>
+      <c r="D20" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
       <c r="A21" s="14" t="s">

--- a/Reports/02_iinuma_sena_作業報告.xlsx
+++ b/Reports/02_iinuma_sena_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="80">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -2148,46 +2148,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Commit のハッシュ値(→の赤丸をしたところの16進数数値）がわかれば、Commitしたときの状態に戻したり、Commitの変更のみ再度適用することはできるので、必要であれば相談してください。</t>
-    <rPh sb="12" eb="13">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>アカマル</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>シン</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>スウチ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>サイド</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>テキヨウ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="89" eb="91">
-      <t>ソウダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2026/5/8(金)</t>
     <rPh sb="9" eb="10">
       <t>キン</t>
@@ -2204,27 +2164,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>朝にデイリースクラムの議事録を行った。
-ゲーム説明を押したときにゲーム説明と操作方法に飛べるようにするのを完了することができました。ボタンを左右に押してページを切り替えることと、タイトルに戻るボタンも動くようになりました。Transfrompositionではなくlocalpositionを使うことで、ボタンを押したときに勝手に動くのを直すことができました。明日は効果音の確認と直しがあれば直せるようにしたいです</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・効果音の切り取り＿途中
-・BGMの実装＿未
-・fainal tester＿未
-・議事録作成(係)</t>
-    <rPh sb="18" eb="20">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・議事録作成ありがとうございました。
 ・残り一日、やれることをやっていきましょう。</t>
     <rPh sb="1" eb="4">
@@ -2238,6 +2177,147 @@
     </rPh>
     <rPh sb="22" eb="24">
       <t>イチニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Commit のハッシュ値(→の赤丸をしたところの16進数数値）
+がわかれば、Commitしたときの状態に戻したり、Commitの変更のみ再度適用することはできるので、必要であれば相談してください。</t>
+    <rPh sb="12" eb="13">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>アカマル</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>サイド</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ソウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音の切り取り＿完了
+・BGMの実装＿完了
+・BGM音量修正＿完了
+・ゲーム説明改良＿改良
+・fainal tester＿完了
+・議事録作成(係)</t>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>オンリョウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カイリョウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>カイリョウ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝にデイリースクラムの議事録を行った。
+ゲーム説明を押したときにゲーム説明と操作方法に飛べるようにするのを完了することができました。ボタンを左右に押してページを切り替えることと、タイトルに戻るボタンも動くようになりました。Transfrompositionではなくlocalpositionを使うことで、ボタンを押したときに勝手に動くのを直すことができました。明日は効果音の確認と直しがあれば直せるようにしたいです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>朝にデイリースクラムの議事録を行った。
+BGMを本プロジェクトに実装してしっかり動くようにできました。また、音量が大きすぎた問題があったのでAudioSouceからVolumを調整してなんとなく聞こえるくらいには調整できました。ゲーム説明やUIで誤字があったので訂正も行いました。Final版として、細かいところが調整できていなかったが、形にはなったのかなと思います。</t>
+    <rPh sb="24" eb="25">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>オンリョウ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>ゴジ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="134" eb="135">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="145" eb="146">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="150" eb="151">
+      <t>コマ</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="169" eb="170">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="179" eb="180">
+      <t>オモ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3074,8 +3154,8 @@
       <c r="D19" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>73</v>
+      <c r="E19" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="108" customHeight="1">
@@ -3083,26 +3163,28 @@
         <v>68</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="9"/>
+      <c r="C21" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="D21" s="10"/>
       <c r="E21" s="8"/>
     </row>
